--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45267</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45918</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44462</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44580</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>44580</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44958</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44918</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45327</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45030</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45887</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45337</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45192</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45856</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45638</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44820</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45327</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45105</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45332</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44953</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45807</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45362</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45350</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45547</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45735</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44855</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44557</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44620</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44498</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44472</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>44588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44610</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>44746</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44557</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44519</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44602</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44466</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44546</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44627</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44480</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44557</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44463</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44598</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44578</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44557</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44467</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44680</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44727</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44623</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44557</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45229</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44557</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44531</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45142</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>45021</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45176</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44964</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45082</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>45635</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44531</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>45142</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44723</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44845</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45022</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45202</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45685</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45643</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45568</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45180</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44949</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45726</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45147</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45674</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45267</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44897</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>44946</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45259</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45541</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45541</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45541</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44981</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44886</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44803</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44742</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44915</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45475</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45539</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45638</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45085</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45227</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45320</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45428</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45015</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45443</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45601</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45686</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>45489</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45316</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44602</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>44937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45252</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45422</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>46030</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45245</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45804</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44539</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44914</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45581</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45331</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44853</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45069</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45268</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45082</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45562</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45203</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45569</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45685</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45896</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45896</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45410</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45923</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45874</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45172</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45029</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45405</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45583</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44852</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>46142</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45680</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45541</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45541</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44466</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45935</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44606</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45632</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45254</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45147</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>46147</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45139</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>45198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>44531</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>44531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>44918</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45156</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45279</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45622</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45246</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45310</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45105</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>44956</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44935</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45807</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44977</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45146</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45966</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>46154</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45966</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45966</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45209</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>44873</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45970</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45973</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45972</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45758</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45758</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45972</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45408</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45408</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45972</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45139</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44459</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45574</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45975</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45271</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45443</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>44519</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>44929</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45243</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45980</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45980</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45386</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>44686</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45435</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45091</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45278</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45179</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45029</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>45733</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46029</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44910</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45993</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45686</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>46163</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45568</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44826</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45965</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45141</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45321</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>46167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45349</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44981</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45727</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45483</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46009</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44557</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44887</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>46029</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46029</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46029</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>46029</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>46029</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>46030</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>46030</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>46030</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46034</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45256</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46042</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46042</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>46042</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44585</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45330</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>46076</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44977</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46176</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45567</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45636</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45273</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46057</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>46058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45331</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45530</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45090</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46182</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>46182</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>46069</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>44593</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46182</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>46182</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45117</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44859</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>44958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>44840</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>46183</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>44460</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>44459</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46084</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46084</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45819</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>45856</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45856</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45538</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45321</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45735</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>46105</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44531</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>46105</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45362</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44930</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45568</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44930</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44896</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44623</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45727</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45205</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45489</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45105</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45373</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>46132</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44742</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>46133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>46133</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46132</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>46132</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46133</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46132</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46132</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>46133</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45727</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45541</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45541</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45820</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45601</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45967</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45939</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44467</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45622</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>46206</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>44958</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>44958</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>46248</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>46205</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>46205</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>46205</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45076</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45076</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>46206</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>44796</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>46205</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45117</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45078</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45210</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45774</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45538</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45541</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45541</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45541</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44953</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45138</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45076</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46258</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>45765</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45541</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45541</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45076</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45316</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45321</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45147</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>44810</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44946</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44593</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45267</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44992</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>46269</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45203</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45310</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>45121</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44489</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45706</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46275</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>46275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>46274</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46274</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45564</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45022</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45699</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46258</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45686</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45643</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45797</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45700</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46241</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45544</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45553</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45615</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>45820</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45821</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>45826</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45835</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45834</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45834</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45834</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45835</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45667</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45848</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45848</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45636</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45243</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45146</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45758</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>44896</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45301</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45124</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44700</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45330</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>44613</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45330</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>44973</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45350</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>45569</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45350</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>44698</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45350</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45470</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45182</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44698</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44841</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45202</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45645</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44676</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44586</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45635</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>44742</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>45205</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>44586</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45761</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45770</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45714</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45715</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>45701</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>45684</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45735</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45805</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45930</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45930</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45973</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45973</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46030</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>46030</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>46077</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46104</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>46155</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45856</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46157</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46205</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45525</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45918</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44929</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44889</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45267</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45887</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45327</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45192</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45337</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45105</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45362</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45327</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44580</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44958</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44953</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44918</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45332</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44472</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44853</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44519</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44480</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44557</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44598</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44578</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44887</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44467</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44680</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44796</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44727</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44700</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44557</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45227</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44810</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45310</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45216</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45422</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45386</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45410</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44557</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45271</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>46029</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46029</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46030</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44531</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44531</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45700</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45483</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44467</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>46030</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>46029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>46029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45797</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45278</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44845</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44531</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46042</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46042</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45896</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45362</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44557</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>46058</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>46057</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44910</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>46069</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45489</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45408</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44896</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44949</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45082</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45408</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45568</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44887</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45541</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45856</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45856</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>46084</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46084</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45819</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45935</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44897</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45142</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>46105</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44489</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44803</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45638</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45256</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45622</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>44946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45966</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44958</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45966</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45966</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45076</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45970</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45972</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>46132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45975</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>46132</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45615</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>46132</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46132</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>46132</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45980</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45980</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45601</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>46133</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>46133</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>46133</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45967</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45674</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45147</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45965</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45939</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45022</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45553</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45820</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>44826</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45443</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>46009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45583</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>46030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45821</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45239</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45643</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44886</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45826</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45082</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45069</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45090</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>46147</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45541</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45834</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45091</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45834</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46154</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45574</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44531</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45835</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45807</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44914</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>46029</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45835</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45105</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45733</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45316</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44539</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45015</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45078</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45686</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46163</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45848</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45667</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45848</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45622</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>46167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45636</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>44956</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45142</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45331</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44585</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45029</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45267</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45538</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45146</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46076</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46176</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45428</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46182</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>46182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45105</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45085</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>44896</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>44977</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45117</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45138</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44531</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45636</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45541</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45541</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45581</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45321</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45569</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45686</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44623</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>45172</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45117</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45179</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45147</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45758</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45685</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45685</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45774</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>46258</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44686</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44853</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45121</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44840</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45266</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45203</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45274</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46265</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44915</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45330</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45349</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45245</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46269</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45726</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44723</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45321</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45310</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46274</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45259</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46275</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46275</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>44539</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>44937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45567</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>44796</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45279</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46258</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46241</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44519</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>44606</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>44897</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>44852</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>44593</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45475</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46287</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44627</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>44946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>46290</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>46290</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45316</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>46289</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45141</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44602</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45541</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45541</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45541</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45568</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44873</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45147</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45180</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45758</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45076</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45320</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45727</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45146</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44466</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45541</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45541</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45735</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45405</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45568</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44977</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45021</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>44958</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44958</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45156</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45243</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45765</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45373</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45331</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44742</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45321</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45205</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>44593</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45632</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45443</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45307</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45680</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44930</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45203</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45562</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45635</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45184</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45538</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45489</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45706</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45022</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45564</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45699</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45686</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45643</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>44700</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>44613</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44698</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44698</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44676</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44586</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>44586</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>45301</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45124</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45330</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44973</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45350</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45569</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45350</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45350</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>45470</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45182</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44841</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45645</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45635</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>44742</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45205</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45761</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45770</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45714</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>45715</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>45684</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45735</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45805</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45973</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45973</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>46030</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>46077</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>46104</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>46155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45856</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46157</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46205</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45525</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45541</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45918</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44929</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44889</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45267</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45887</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45327</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45192</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45337</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45105</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>45846</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45362</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45327</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44580</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44958</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44953</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44918</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45332</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44472</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44853</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44519</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44480</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44557</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44598</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44578</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44887</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44467</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44680</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44796</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44727</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44700</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44557</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45227</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44810</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45310</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45216</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45422</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>45435</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45386</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45410</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44557</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>45139</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45271</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>46029</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>46029</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>46030</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44531</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44531</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45700</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45483</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44467</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>46030</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>46029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>46029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>46029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45797</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45278</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44845</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44531</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46042</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46042</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45896</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45896</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45362</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44896</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44557</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>46058</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>46057</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44910</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>46069</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45489</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45408</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44896</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44949</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45082</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45408</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45568</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44887</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45541</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45856</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45856</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>46084</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46084</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45819</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45935</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44897</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45142</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>46105</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44489</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44803</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45638</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45256</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45622</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>44946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>45966</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44958</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44958</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45966</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45966</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45076</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45970</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45972</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>46132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45975</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>46132</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45615</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>46132</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46132</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>46132</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45980</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45980</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45601</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>46133</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>46133</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>46133</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45967</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45674</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45147</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45965</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45939</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45022</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45553</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45820</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>44826</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45443</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>46009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45583</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>46030</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45821</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45239</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45643</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44886</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45826</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45082</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45727</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45069</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45090</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>46147</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44929</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45541</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45834</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45091</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45834</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46154</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45574</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44531</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45835</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45807</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44914</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>46029</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45835</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45105</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45733</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45316</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44539</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45015</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45078</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45686</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46163</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45848</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45667</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45848</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45622</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>46167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45636</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>44956</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45142</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45331</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44585</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45029</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45267</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45538</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45146</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46076</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46176</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45428</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46182</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>46182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45105</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45085</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>44896</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>44977</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45117</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>44953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45138</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44531</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45636</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45541</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45541</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45581</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45321</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45569</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45686</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44623</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>45172</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45117</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45179</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45147</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45758</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45685</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45685</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45774</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>46258</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44686</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44853</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45198</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45121</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44840</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45266</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45203</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45274</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46265</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44915</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45330</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45349</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45245</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46269</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45726</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44723</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45321</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45310</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>46274</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45259</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>46275</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46275</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>44539</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>44937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45567</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>44796</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45279</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46258</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46241</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44519</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>44606</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>44897</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>44852</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>44593</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45475</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46287</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44627</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>46248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>44946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>46290</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>46290</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45316</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>46289</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45141</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44602</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45541</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45541</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45541</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45568</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44873</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45147</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45180</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45758</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45076</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45320</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45727</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45146</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44466</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45541</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45541</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45735</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45405</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45568</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45254</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44977</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45021</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>44958</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44958</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45156</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45243</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45765</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45373</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45331</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>44742</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45321</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45205</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>44593</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45632</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45443</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>45307</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45680</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44930</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45203</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>45562</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45635</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45184</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45538</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45489</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45706</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45022</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45564</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45699</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45686</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45643</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>44700</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>44613</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44698</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44698</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44676</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44586</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>44586</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>45301</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45124</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>45330</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>45330</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>44973</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45350</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45569</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45350</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45350</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>45470</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>45182</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44841</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45645</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45635</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>44742</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45205</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45761</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45770</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45714</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>45715</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>45684</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45735</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45805</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45973</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45973</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>46030</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>46077</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>46104</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>46155</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45856</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45267</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45327</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45030</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45327</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45856</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45527</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45362</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45337</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45192</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44820</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45076</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45105</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45332</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45390</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44472</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44853</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44519</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44480</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44598</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44578</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44886</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44680</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44700</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>44623</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44557</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45229</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44557</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45176</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45142</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45082</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44531</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45021</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45635</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45142</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44723</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45022</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45022</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45643</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45202</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45699</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45568</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>46009</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45686</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45726</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>46029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>46029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>46029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>46030</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46030</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>45674</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45267</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44958</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45259</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44897</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45797</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45274</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45918</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46057</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46058</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44742</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45935</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>44803</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46069</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45188</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45475</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45539</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45638</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45544</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45085</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>46084</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45227</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45856</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45856</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45320</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45428</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45966</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45015</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45970</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45972</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45252</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45972</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45443</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>46105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45601</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45980</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45489</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45686</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45980</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45820</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>44937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45316</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45422</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45821</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>44627</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45993</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45245</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>44539</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45216</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45826</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44914</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45638</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>46132</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46133</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>46132</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>46133</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>46132</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45331</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44853</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45835</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45834</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45834</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45082</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45203</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45569</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45820</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45685</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45410</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46030</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45667</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45848</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45848</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45172</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45405</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44958</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44852</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45243</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45680</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45541</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45541</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44606</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45632</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45254</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45147</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45139</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45146</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>44897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44531</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44918</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45758</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45583</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45279</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>46142</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>46147</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45622</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45310</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45105</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44956</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45807</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>46154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44977</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45239</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>45146</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45574</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>45909</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45209</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44873</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45733</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45686</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45758</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45758</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45408</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45408</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>46163</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>46163</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45271</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45443</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44937</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44519</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>46167</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45243</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45386</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44686</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45435</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45278</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45179</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45029</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44585</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44910</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>46076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>46176</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45568</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46182</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>46182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>46182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44826</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>46183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45141</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45321</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45349</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45727</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45483</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>44557</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44887</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45256</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46205</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46205</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46205</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45147</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45330</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>46258</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46258</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44977</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45567</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>46265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45273</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45331</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45530</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45090</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45117</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44859</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44840</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46275</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>46275</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46274</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45538</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>46241</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45321</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45735</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45362</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>44930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45568</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44930</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46287</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>44896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46289</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44623</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45727</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45489</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45373</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46290</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45203</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44887</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45758</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>46248</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>46290</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45541</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45541</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45601</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46294</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45622</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44958</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45574</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44796</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45117</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45078</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45774</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45538</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45541</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45541</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44953</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>45138</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45076</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45765</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45541</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45541</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45316</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45321</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45147</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>44810</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>44946</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>44992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45121</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44489</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45706</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45564</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45301</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45124</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>44700</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45330</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44613</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45330</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44973</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>45350</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45569</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>45350</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>44698</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45350</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>45470</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>44698</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>44841</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45202</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45645</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>44676</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44586</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45635</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44742</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45205</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>44586</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45761</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45770</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45715</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45701</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45684</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45735</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45805</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45930</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45930</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45973</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>46077</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>46104</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45856</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45267</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45327</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45030</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45327</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45856</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45527</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45362</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45337</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45192</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44820</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45076</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45105</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45332</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45390</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44472</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44557</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44853</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44519</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44546</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44480</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44598</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44578</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44886</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44680</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44700</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>44623</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44557</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45229</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44557</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45176</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45142</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45082</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>44531</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45021</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45635</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45142</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44723</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45022</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45180</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45022</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45643</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45202</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45699</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45568</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>46009</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45686</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45726</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>46029</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>46029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>46029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>46030</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46030</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45896</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>45674</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45267</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44958</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45259</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44897</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45797</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45274</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45918</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44886</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46057</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46058</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44742</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45935</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>44803</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46069</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45188</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>44915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45475</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45539</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45638</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45544</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45085</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>46084</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45227</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45856</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45856</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45320</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45428</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45966</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45966</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45015</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45970</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45973</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45972</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45252</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45972</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45443</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45975</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>46105</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45601</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45553</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45980</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45489</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45686</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45980</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45980</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45615</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45820</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>44937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45316</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45422</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45821</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>44627</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45993</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45245</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>44539</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45216</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45826</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44914</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45638</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45581</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>46132</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46133</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46132</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>46132</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>46133</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>46132</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45331</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44853</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45835</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45834</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45834</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45082</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45203</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45569</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45820</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45685</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45939</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45410</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46030</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45667</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45848</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45848</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45172</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45405</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>44958</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>44852</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>45874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45243</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45680</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45541</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45541</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44606</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45632</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45254</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45147</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45139</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45198</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45146</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>44897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45069</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44531</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44918</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45758</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45583</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45279</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>46142</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>46147</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45622</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45310</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45105</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44956</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45807</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>46154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44977</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45239</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>45146</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45574</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>45909</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45209</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44873</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45733</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45686</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45758</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45758</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45408</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45408</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45139</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>46163</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>46163</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45271</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45443</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44937</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44519</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>46167</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>45243</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45386</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44686</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45435</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45278</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45179</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>45029</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44585</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>44910</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>46076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>46176</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45568</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>46182</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>46182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>46182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44826</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>46183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45141</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45321</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45349</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45727</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45483</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>44557</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>44887</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45256</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46206</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>46205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>46205</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>46205</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>46206</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46205</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45147</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45330</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>46258</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46258</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44977</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45567</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>46265</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45273</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45331</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45530</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45090</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45266</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45117</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>44859</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44840</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46275</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>46275</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46274</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46274</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45538</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>46241</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45321</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45735</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45362</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>44930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45568</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44930</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46287</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>44896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46289</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44623</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45727</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45205</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45489</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45373</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46290</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45203</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44887</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45758</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>46248</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>46290</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45727</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>45541</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45541</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45601</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46294</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45622</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44958</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44958</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45574</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45076</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44796</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45117</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45078</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45774</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45538</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45541</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45541</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44953</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>45138</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45076</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45765</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45541</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45541</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45316</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45321</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45147</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>44810</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>44946</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45267</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>44992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45310</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45121</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>44489</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45706</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45564</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45301</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45124</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>44700</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45330</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44613</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45330</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44973</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>45350</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45569</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>45350</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>44698</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45350</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>45470</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>44698</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>44841</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45202</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45645</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>44676</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44586</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45635</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44742</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45205</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>44586</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45761</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45770</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45715</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45701</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45684</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45735</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45805</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45930</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45930</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45973</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>46077</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>46104</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46157</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46205</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44889</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45541</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45827</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45076</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45846</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45327</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45887</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45527</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45332</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45638</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45192</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45807</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45856</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44958</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45076</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45337</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45327</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44588</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44598</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44680</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44480</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44578</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44810</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44700</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44557</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45310</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45541</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45541</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45091</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45422</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45216</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44958</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>44958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45435</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44914</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45105</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45227</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45156</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45316</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44937</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45386</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45243</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45765</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45410</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45078</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45373</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44557</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45069</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45331</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44742</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45622</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45574</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45321</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44956</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45142</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45267</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44896</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45205</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44593</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45632</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45443</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45307</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45680</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45271</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45331</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45483</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45252</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45727</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45562</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44981</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45176</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45278</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44845</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45209</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45184</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45538</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44531</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44531</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45538</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44887</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44992</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45428</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45362</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45909</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45105</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44896</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45085</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45601</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44557</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45139</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45918</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44953</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45541</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44910</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45022</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45138</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45564</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45408</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45699</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44949</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45686</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45082</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45643</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45408</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45568</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44887</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45541</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45541</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45321</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45935</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45142</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44930</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45569</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45686</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>44623</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45076</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45076</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45172</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45544</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>44964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44489</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45117</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45179</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45147</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45758</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45638</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45256</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45553</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45685</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45685</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44958</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45774</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44946</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45826</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45831</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45834</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45834</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45835</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45835</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>44686</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44742</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44853</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45121</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44840</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45266</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45203</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45674</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45970</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45727</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45147</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45848</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45667</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45848</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45636</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45147</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45243</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45022</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45349</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45245</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45726</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44723</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45758</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45321</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>45980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45310</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44896</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44935</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45443</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45259</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45643</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44937</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44886</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45567</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>44796</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45539</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>46105</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>46105</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>45082</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45268</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45727</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45069</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45993</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44519</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44606</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46132</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44897</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44852</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46133</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46133</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45475</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46133</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45967</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>45804</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44627</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45874</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45316</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45820</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>46009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45141</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44602</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45923</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45541</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45541</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45541</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46029</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46029</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46030</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46030</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45568</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44873</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>46030</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46029</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46029</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46034</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45147</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45180</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45758</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45076</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45320</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46042</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>46042</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45146</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45583</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45541</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>46030</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45541</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45735</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45405</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45568</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45254</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>44977</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46057</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>46142</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>46147</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>46069</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45246</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46154</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45856</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45856</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46084</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45574</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45909</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45807</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45733</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45686</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46163</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46163</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44585</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>46076</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>46176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46182</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>46182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>46182</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46183</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>46205</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>46205</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46269</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>46274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46275</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>46275</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>46241</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46287</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>46290</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>46290</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46294</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>46248</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>46299</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>46297</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>46163</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>46258</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>46274</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46258</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45821</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46304</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44700</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44613</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44698</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44676</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44586</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44586</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45301</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45124</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45330</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45330</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44973</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45350</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45569</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45350</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45350</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45470</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45182</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44841</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45202</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44742</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45761</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45770</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45714</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45715</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45701</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45684</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45735</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45805</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45930</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45930</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45973</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>46030</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>46077</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46155</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46157</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46205</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44889</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45541</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45267</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45827</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45076</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45846</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44820</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45327</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45887</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45527</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45332</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45638</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45192</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45807</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45856</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45362</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44958</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>44953</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44918</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45076</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45337</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45327</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44588</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44598</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44627</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44680</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44480</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44886</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44578</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44810</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44700</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>44929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44557</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45021</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45310</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45541</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45541</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45091</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45422</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45216</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44958</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>44958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45435</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>44914</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45105</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45227</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45156</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45316</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44937</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45386</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45243</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45765</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45410</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>45078</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45373</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44557</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>45069</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45331</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44742</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45622</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45574</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45229</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45321</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44956</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45142</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45267</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44896</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45205</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44593</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45632</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45443</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45307</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45680</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45271</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45331</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45483</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45252</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45727</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45562</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44981</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>45176</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45635</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45278</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44845</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45209</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45184</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45538</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44531</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44531</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45538</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44887</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44992</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45428</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45530</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45362</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45909</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45105</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44896</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45085</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45601</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44557</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45139</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45918</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44953</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45541</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44910</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45022</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45138</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45564</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45408</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45699</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44949</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45686</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45082</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45643</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45408</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45568</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44887</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45541</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45541</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45797</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>44897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45321</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45935</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45142</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44930</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45569</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45686</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>44623</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45076</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45076</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45172</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45544</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>44964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44489</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45117</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>45179</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45147</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45758</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45638</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45256</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45553</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45622</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45685</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45685</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44958</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45774</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44946</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45826</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>45831</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45834</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45834</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45834</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45835</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45835</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>44686</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44742</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44853</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45121</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44840</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45266</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45203</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45674</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45970</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45727</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45147</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>45848</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45667</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45848</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45636</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45147</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45243</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45022</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45349</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45245</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45726</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44723</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45758</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45321</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45980</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>45980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45310</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44896</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>44935</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45443</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45259</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>45239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>45643</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44937</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44886</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45567</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>44796</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45539</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>46105</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>46105</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>45082</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45268</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44918</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45727</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45069</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45993</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44519</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44606</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46132</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44897</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44852</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46133</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46133</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45475</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46133</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45967</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>45804</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44627</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45874</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45316</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45820</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>46009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45141</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44602</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45923</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45541</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45541</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45541</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46029</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46029</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46030</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>46030</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45568</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44873</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>46030</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>46029</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46029</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46034</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45147</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45180</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45758</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45758</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45076</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45320</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>46042</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>46042</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45146</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45583</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45541</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>46030</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45541</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45735</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45405</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45568</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45254</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>44977</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>46058</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46057</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>46142</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>46147</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>46069</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45246</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46154</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45856</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45856</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46084</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45574</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45909</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45819</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45807</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45733</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45686</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46163</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46163</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44585</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>46076</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>46176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46182</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>46182</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>46182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>46182</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46183</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46205</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>46205</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>46205</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46269</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>46274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>46275</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>46275</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>46241</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46287</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>46290</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>46290</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46294</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>46248</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>46299</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>46297</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>46163</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>46258</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>46274</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>46258</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45821</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>46304</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44700</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44613</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44698</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44698</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44676</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44586</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44586</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45301</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45124</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45330</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45330</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44973</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45350</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45569</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45350</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45350</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45470</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45182</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44841</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45202</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45645</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44742</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45761</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45770</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45714</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45715</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45701</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45684</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45735</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45805</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45930</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45930</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45973</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>46030</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>46077</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46104</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46155</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45918</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45267</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45327</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45337</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45192</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45327</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44820</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45105</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45332</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44953</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45807</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45362</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45390</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44557</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44546</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44627</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44557</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44598</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44680</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44727</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44700</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45229</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44557</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44531</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44531</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45021</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45082</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45176</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45635</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45142</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44723</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45307</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44845</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45022</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45685</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45643</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45568</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44949</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45727</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45674</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45267</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45541</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45274</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44886</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44803</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45539</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>45085</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45227</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45428</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45320</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45015</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45252</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45601</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45686</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45489</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>46030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45316</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45422</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44627</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44539</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44914</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45581</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45923</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45331</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44853</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45082</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45562</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45203</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45569</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45583</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45685</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46142</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45410</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>46147</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45918</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45246</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45935</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45172</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45405</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44852</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45807</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>46154</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45680</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45541</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45541</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45574</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45254</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45147</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45909</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45139</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45184</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45733</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46029</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44531</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44918</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45156</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45645</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45686</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45966</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45279</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45970</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46163</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45622</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45310</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>44956</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45980</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>46167</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44935</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45980</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45980</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45239</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45146</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45209</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44873</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45758</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45408</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45408</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45139</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45271</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45443</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>44937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44519</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44929</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45243</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45386</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45435</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45278</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45179</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45029</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44910</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44585</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45568</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>46029</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46029</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>46029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46029</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44826</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46030</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45141</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>46076</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45321</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45349</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45727</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45483</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46057</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>44557</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44887</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45256</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46084</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45819</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45856</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45856</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45147</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45330</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44539</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44977</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45567</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>46105</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45636</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>46105</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45273</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45331</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45530</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45090</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44593</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45266</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45117</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44859</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>44840</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>46133</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>46132</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>46132</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>46133</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46132</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45820</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45967</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45939</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45538</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46205</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46205</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46206</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46205</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45321</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45735</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45362</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45568</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>44930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44896</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>44623</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45727</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45205</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45489</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45105</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46275</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45373</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>44742</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46274</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45541</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45541</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45601</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45622</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>44958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45574</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45076</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44796</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45117</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45078</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45210</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46287</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45774</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45538</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45541</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45541</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44953</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45138</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45076</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45765</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>46290</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45541</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45541</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46248</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45316</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45321</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45147</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44810</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44946</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46294</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44593</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46297</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44992</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45310</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45121</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>44489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46163</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45706</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>46299</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45564</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45821</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46274</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45022</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45699</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45686</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45643</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45797</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46304</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46308</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45544</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>46269</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45553</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45615</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45826</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45831</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45835</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45834</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45834</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45835</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45667</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45848</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45848</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45243</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45146</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45758</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44896</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>45301</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45124</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45330</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44613</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45330</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44973</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45350</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45569</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45350</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44698</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45350</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45470</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45182</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>44698</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>44841</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45202</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45645</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44676</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>44586</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44742</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>44586</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45761</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45770</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45714</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45715</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45701</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45684</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45735</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45805</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45930</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45930</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45973</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46077</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46104</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46155</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46157</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45267</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45918</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45267</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44965</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45076</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>45541</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45525</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>44958</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45327</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45337</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>45192</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45327</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44820</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45105</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45332</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44953</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45807</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45362</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45846</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45390</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44557</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44546</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44627</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44557</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44598</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44680</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44727</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44700</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45229</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44557</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44531</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44531</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45142</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45021</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45082</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45176</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45635</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45142</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44723</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45307</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44845</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45022</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45685</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45643</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45568</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45726</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44949</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45727</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45674</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45267</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45541</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45274</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44886</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44803</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45539</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>45085</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45227</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45428</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45320</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45015</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45252</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45601</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45686</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45489</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>46030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45316</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>45422</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>44627</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44539</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45216</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44914</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45581</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45923</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45331</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44853</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45082</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45562</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>44896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45203</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45569</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45583</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45685</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46142</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45410</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>46147</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45918</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45246</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45935</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45172</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45405</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44852</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45807</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>46154</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45680</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45541</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45541</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45574</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45254</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45147</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45909</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45139</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45184</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45733</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46029</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44897</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44531</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44918</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45156</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45645</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45686</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45966</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45279</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45970</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46163</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45622</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45310</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>44956</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45980</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>46167</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44935</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45980</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45980</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45239</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45146</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45209</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44873</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45758</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45758</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45408</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45408</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45139</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45271</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45443</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>44937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>44519</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44929</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45243</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45386</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44686</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45435</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45091</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45278</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45179</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45029</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44910</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44585</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45568</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>46029</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46029</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>46029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46029</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44826</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46030</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45141</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>46076</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45321</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45349</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46042</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45727</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45483</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>46057</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>46183</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>44557</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44887</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45256</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46084</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45819</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45856</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45856</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45147</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45330</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44539</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44977</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45567</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>46105</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45636</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>46105</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45273</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45331</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45530</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45090</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44593</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45266</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45117</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>44859</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>44840</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>46133</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>46132</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>46132</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>46133</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46132</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45820</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45967</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45939</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45538</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>46205</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>46205</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>46206</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>46205</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45321</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45735</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45362</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45568</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>44930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>44896</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>44623</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45727</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>45205</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45489</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45105</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46275</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45373</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>44742</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46274</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45758</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45541</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45541</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45601</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45622</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>44958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45574</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45076</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44796</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45117</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45078</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45210</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46287</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46289</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45774</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45538</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45541</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45541</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44953</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45138</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45076</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45765</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>46290</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45541</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45541</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45076</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46248</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>46290</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45316</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45321</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45147</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44810</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44946</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46294</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44593</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46297</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44992</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45310</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45121</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>44489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46163</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45706</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>46299</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45564</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>45821</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>46274</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45022</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45699</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45686</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46258</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45643</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45797</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45700</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46304</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46308</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>46265</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45544</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>46269</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45553</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45615</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45826</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45831</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45835</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45834</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45834</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45835</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45667</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45848</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45848</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45243</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45146</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45758</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44896</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>45301</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>45124</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45330</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44613</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45330</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44973</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45350</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45569</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45350</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44698</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45350</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45470</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45182</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>44698</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>44841</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45202</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45645</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44676</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>44586</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44742</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45205</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>44586</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45761</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45770</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45714</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45715</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45701</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45684</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45735</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45805</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45930</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45930</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45973</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46077</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46104</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46155</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46157</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46205</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45267</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45512</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45541</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>44929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44965</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45267</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45887</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44820</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45856</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45332</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>45327</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45527</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45192</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45337</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45105</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45327</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44580</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44958</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44557</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44546</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44627</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44557</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44598</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44680</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45227</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44946</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45316</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45069</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>45541</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45541</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45733</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45568</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44873</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45686</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45180</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45758</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45918</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45076</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45320</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45210</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45310</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45146</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44585</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45735</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45405</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45935</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45254</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45422</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44977</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45216</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45435</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>46076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>46176</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45386</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45410</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>46182</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45156</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45243</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45765</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45966</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45373</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45966</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45331</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44742</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45321</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45970</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45205</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45975</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45229</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45443</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45307</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45980</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45980</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45680</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44930</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46206</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46205</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45203</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45727</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45562</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44896</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45176</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45184</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45139</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45538</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45489</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45638</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45706</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45022</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45564</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46029</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>46030</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>46030</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>46030</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>46029</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>46029</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>46034</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45699</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>45686</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45643</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>46241</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45797</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>46287</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46290</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46290</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>46289</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>46058</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>46057</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44531</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>46294</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>46069</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45483</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>46248</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45553</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45826</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45856</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45856</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46084</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45834</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>46084</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45819</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45834</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45835</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>46299</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45835</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46163</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45848</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>46105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45667</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45848</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45636</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46258</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45243</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45821</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45278</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44845</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45146</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46304</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45758</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44531</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44531</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46258</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46132</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>46132</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44887</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46132</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46132</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>46132</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44929</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45530</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45362</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46133</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46133</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46307</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46133</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45967</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44557</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45923</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45541</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45939</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46314</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>46269</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44910</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45489</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45408</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44896</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44949</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45082</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45583</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>46315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45408</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45568</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>46315</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44887</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45541</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46275</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46142</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44937</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46274</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44897</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46275</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46147</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45142</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45246</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45574</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45909</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45807</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44803</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46029</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45638</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45256</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45622</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44958</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44958</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45601</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45674</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45727</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45147</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45147</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45022</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44826</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45443</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45239</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45643</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45203</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45082</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45268</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44918</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45727</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45090</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45541</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45541</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45091</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44914</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45316</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>44937</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45015</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45078</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45622</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45574</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44956</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45142</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45331</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45029</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45209</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45538</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45428</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45085</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45601</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44981</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44977</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45117</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44953</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45138</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>44531</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45636</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45202</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45541</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45541</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45581</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45321</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45569</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45686</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44623</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45076</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45076</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45172</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45117</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45179</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45147</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45685</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45774</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44686</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>44742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44853</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45121</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>44915</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45349</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45245</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45726</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44723</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45321</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45310</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44935</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45259</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44539</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44937</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45567</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44519</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44606</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44897</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44852</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44613</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44698</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44698</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44676</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44586</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44586</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45301</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45124</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45330</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45330</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>44973</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45350</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45569</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45350</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45350</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45470</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44841</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45635</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44742</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45205</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45761</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45770</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45714</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45715</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45701</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45684</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45735</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45805</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45930</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45973</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46077</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46104</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46155</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>

--- a/Översikt ÖSTRA GÖINGE.xlsx
+++ b/Översikt ÖSTRA GÖINGE.xlsx
@@ -601,7 +601,7 @@
         <v>45330</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44634</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>46167</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45637</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>44897</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44586</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>44964</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46157</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46205</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>45267</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45330</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45783</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45076</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45846</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45512</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45541</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>44929</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44965</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45267</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44967</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45730</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45923</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>44580</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45887</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44918</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>45076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44820</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45856</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45332</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>45327</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>45527</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45192</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45337</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45105</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45327</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44580</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44958</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44973</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45390</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45350</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44973</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45735</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44620</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44498</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44557</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44746</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44557</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44853</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44546</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44627</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44557</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44598</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44680</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44796</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44727</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44627</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45227</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>44946</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45316</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45069</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>45141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>44810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>45541</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>45541</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45541</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>45733</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>45568</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44873</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45686</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45147</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45180</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45758</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45918</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45076</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45320</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46167</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45210</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45310</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45146</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44585</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45735</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45405</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45935</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45254</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45422</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44977</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45216</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45435</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>46076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>46176</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45386</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44859</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45410</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>46182</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44557</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>46182</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45156</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45243</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45765</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45966</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45373</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45966</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45331</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44742</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45321</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45970</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45205</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45975</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45229</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45443</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45307</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45980</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45980</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45680</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44930</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46206</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46205</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45203</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45252</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46206</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45727</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45562</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44896</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45176</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45184</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>45139</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45538</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45489</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45638</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45706</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>46009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45022</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45564</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46029</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>46030</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>46030</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>46030</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>46029</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>46029</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>46034</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45699</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>45686</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45643</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>46241</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45797</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>46287</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46290</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46290</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>46289</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>46058</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>46057</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44531</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>46294</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>46069</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45483</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>46248</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45553</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45826</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45856</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45856</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46084</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45834</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>46084</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45819</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45834</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45835</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>46299</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45835</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>46297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46163</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45848</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>46105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45667</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45848</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45636</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46258</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45243</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45821</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45278</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>44845</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45146</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46304</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45758</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44531</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44896</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44531</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46258</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46132</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>46132</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44887</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46132</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46132</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>46132</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44929</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45530</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45362</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46133</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46133</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46307</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46133</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45967</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45874</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>44557</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45923</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45541</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45939</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46314</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>46269</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44910</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45489</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45408</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44896</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44949</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45082</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45583</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>46315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45408</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45568</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>46315</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44887</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45541</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46275</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46142</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44937</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46274</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44897</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>46275</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46147</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45142</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45246</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46154</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45574</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>45909</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>45807</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>44803</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46029</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45638</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45256</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45622</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44958</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44958</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>45601</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45674</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45727</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45147</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45147</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>45022</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44826</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45443</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45239</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45643</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45203</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45539</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45082</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45268</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44918</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45727</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45090</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45541</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45541</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45091</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44531</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44914</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45105</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45316</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>44539</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>44937</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45015</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45078</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45622</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45574</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44956</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45142</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45331</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45029</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45209</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45538</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45428</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45085</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45601</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44981</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44977</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45117</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44953</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45138</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>44531</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>45636</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45202</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>45541</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45541</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45581</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45321</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45569</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45686</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44623</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45076</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45076</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45172</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45117</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45179</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45147</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45685</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45774</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>44686</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>44742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44853</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45121</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45274</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>44915</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45349</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45245</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45726</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44723</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45321</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45310</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44935</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45259</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>44539</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>45273</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>44937</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45567</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44519</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44606</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44897</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44852</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>44700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>44613</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44698</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44698</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>44676</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44586</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44586</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45301</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45124</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45330</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45330</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>44973</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45350</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45569</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45350</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>45350</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45470</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44841</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45635</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44742</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45205</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45761</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>45770</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>45714</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45715</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45701</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45684</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45735</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45805</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45930</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45930</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45973</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45973</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46077</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>46104</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>46155</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
